--- a/RxForEyeIPD/Files/02. WithoutPrimaryAndWithForeignKey/TableCreateWithoutPrimaryAndWithForeignKey.xlsx
+++ b/RxForEyeIPD/Files/02. WithoutPrimaryAndWithForeignKey/TableCreateWithoutPrimaryAndWithForeignKey.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="4"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="NF_DataAnnotation" sheetId="6" r:id="rId1"/>

--- a/RxForEyeIPD/Files/02. WithoutPrimaryAndWithForeignKey/TableCreateWithoutPrimaryAndWithForeignKey.xlsx
+++ b/RxForEyeIPD/Files/02. WithoutPrimaryAndWithForeignKey/TableCreateWithoutPrimaryAndWithForeignKey.xlsx
@@ -9,14 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="NF_DataAnnotation" sheetId="6" r:id="rId1"/>
     <sheet name="NF_Datatype" sheetId="5" r:id="rId2"/>
     <sheet name="TblDistrictMaster" sheetId="7" r:id="rId3"/>
     <sheet name="TblBranchUnit" sheetId="8" r:id="rId4"/>
-    <sheet name="TblUser" sheetId="9" r:id="rId5"/>
+    <sheet name="TblUsers" sheetId="9" r:id="rId5"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -125,7 +125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E8" authorId="0" shapeId="0">
+    <comment ref="E13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -145,7 +145,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="200">
   <si>
     <t>SlNo</t>
   </si>
@@ -1405,15 +1405,9 @@
     <t>UserName</t>
   </si>
   <si>
-    <t>BranchId</t>
-  </si>
-  <si>
     <t>UserId</t>
   </si>
   <si>
-    <t>User</t>
-  </si>
-  <si>
     <t>BaseHospital</t>
   </si>
   <si>
@@ -1421,6 +1415,45 @@
   </si>
   <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>Users</t>
+  </si>
+  <si>
+    <t>UserRoleId</t>
+  </si>
+  <si>
+    <t>TblUserRole</t>
+  </si>
+  <si>
+    <t>UserRoleName</t>
+  </si>
+  <si>
+    <t>UserPassword</t>
+  </si>
+  <si>
+    <t>VarChar</t>
+  </si>
+  <si>
+    <t>VarBinary</t>
+  </si>
+  <si>
+    <t>NVarChar</t>
+  </si>
+  <si>
+    <t>ScreenSize</t>
+  </si>
+  <si>
+    <t>DeviceName</t>
+  </si>
+  <si>
+    <t>Manufacturer</t>
+  </si>
+  <si>
+    <t>IpAddress</t>
+  </si>
+  <si>
+    <t>(30)</t>
   </si>
 </sst>
 </file>
@@ -3154,13 +3187,13 @@
         <v>159</v>
       </c>
       <c r="J4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K4" t="s">
         <v>175</v>
       </c>
       <c r="L4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M4" s="14"/>
     </row>
@@ -3650,7 +3683,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultColWidth="12" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="13.85546875" customWidth="1"/>
@@ -3713,7 +3746,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>32</v>
@@ -3742,7 +3775,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -3780,7 +3813,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
@@ -3795,19 +3828,19 @@
         <v>12</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I4" t="s">
         <v>159</v>
       </c>
       <c r="J4" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="K4" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="L4" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="M4" s="14"/>
     </row>
@@ -3822,7 +3855,7 @@
         <v>182</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>194</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>171</v>
@@ -3863,7 +3896,7 @@
         <v>180</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>192</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>171</v>
@@ -3904,13 +3937,16 @@
         <v>178</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>193</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>164</v>
       </c>
       <c r="F7" t="s">
-        <v>162</v>
+        <v>13</v>
+      </c>
+      <c r="G7" t="s">
+        <v>12</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>156</v>
@@ -3934,16 +3970,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>191</v>
       </c>
       <c r="D8" t="s">
-        <v>8</v>
+        <v>193</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>32</v>
+        <v>164</v>
       </c>
       <c r="F8" t="s">
         <v>10</v>
@@ -3966,22 +4002,23 @@
       <c r="L8" t="s">
         <v>156</v>
       </c>
+      <c r="M8" s="14"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>196</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>32</v>
+        <v>199</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
@@ -4004,22 +4041,23 @@
       <c r="L9" t="s">
         <v>156</v>
       </c>
+      <c r="M9" s="14"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>195</v>
       </c>
       <c r="D10" t="s">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>32</v>
+        <v>171</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
@@ -4042,28 +4080,29 @@
       <c r="L10" t="s">
         <v>156</v>
       </c>
+      <c r="M10" s="14"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>197</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>32</v>
+        <v>199</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>156</v>
@@ -4080,22 +4119,23 @@
       <c r="L11" t="s">
         <v>156</v>
       </c>
+      <c r="M11" s="14"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>198</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>32</v>
+        <v>171</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
@@ -4118,6 +4158,7 @@
       <c r="L12" t="s">
         <v>156</v>
       </c>
+      <c r="M12" s="14"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13">
@@ -4127,16 +4168,16 @@
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G13" t="s">
         <v>12</v>
@@ -4165,33 +4206,223 @@
         <v>26</v>
       </c>
       <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I14" t="s">
+        <v>156</v>
+      </c>
+      <c r="J14" t="s">
+        <v>156</v>
+      </c>
+      <c r="K14" t="s">
+        <v>156</v>
+      </c>
+      <c r="L14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I15" t="s">
+        <v>156</v>
+      </c>
+      <c r="J15" t="s">
+        <v>156</v>
+      </c>
+      <c r="K15" t="s">
+        <v>156</v>
+      </c>
+      <c r="L15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I16" t="s">
+        <v>156</v>
+      </c>
+      <c r="J16" t="s">
+        <v>156</v>
+      </c>
+      <c r="K16" t="s">
+        <v>156</v>
+      </c>
+      <c r="L16" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I17" t="s">
+        <v>156</v>
+      </c>
+      <c r="J17" t="s">
+        <v>156</v>
+      </c>
+      <c r="K17" t="s">
+        <v>156</v>
+      </c>
+      <c r="L17" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I18" t="s">
+        <v>156</v>
+      </c>
+      <c r="J18" t="s">
+        <v>156</v>
+      </c>
+      <c r="K18" t="s">
+        <v>156</v>
+      </c>
+      <c r="L18" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
         <v>20</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D19" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F19" t="s">
         <v>10</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G19" t="s">
         <v>24</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="I14" t="s">
-        <v>156</v>
-      </c>
-      <c r="J14" t="s">
-        <v>156</v>
-      </c>
-      <c r="K14" t="s">
-        <v>156</v>
-      </c>
-      <c r="L14" t="s">
+      <c r="H19" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I19" t="s">
+        <v>156</v>
+      </c>
+      <c r="J19" t="s">
+        <v>156</v>
+      </c>
+      <c r="K19" t="s">
+        <v>156</v>
+      </c>
+      <c r="L19" t="s">
         <v>156</v>
       </c>
     </row>
